--- a/data/Lüterkofen-Ichertswil/investment_decision/Ichertswil_MFH_from_2015_investment_decision.xlsx
+++ b/data/Lüterkofen-Ichertswil/investment_decision/Ichertswil_MFH_from_2015_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>7.058892288634488</v>
+        <v>1.271441376778455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>1828.331536744552</v>
       </c>
       <c r="F2" t="n">
-        <v>7.058892288634488</v>
+        <v>1.305942291935749</v>
       </c>
       <c r="G2" t="n">
         <v>1828.331536744552</v>
       </c>
       <c r="H2" t="n">
-        <v>7.251453505656018</v>
+        <v>1.271441376778454</v>
       </c>
       <c r="I2" t="n">
         <v>1828.331536744552</v>
       </c>
       <c r="J2" t="n">
-        <v>7.251453505656016</v>
+        <v>1.271441376778455</v>
       </c>
       <c r="K2" t="n">
         <v>1828.331536744552</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>11.6544026053454</v>
+        <v>4.548273152700986</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>1828.331536744552</v>
       </c>
       <c r="F3" t="n">
-        <v>11.54713229285424</v>
+        <v>4.834333849950032</v>
       </c>
       <c r="G3" t="n">
         <v>1828.331536744552</v>
       </c>
       <c r="H3" t="n">
-        <v>13.68257971060883</v>
+        <v>4.57440556663083</v>
       </c>
       <c r="I3" t="n">
         <v>1828.331536744552</v>
       </c>
       <c r="J3" t="n">
-        <v>13.68257971060883</v>
+        <v>4.775730570662059</v>
       </c>
       <c r="K3" t="n">
         <v>1828.331536744552</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>11.6544026053454</v>
+        <v>4.757116543224582</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>1828.331536744552</v>
       </c>
       <c r="F4" t="n">
-        <v>11.54713229285424</v>
+        <v>4.834333849950005</v>
       </c>
       <c r="G4" t="n">
         <v>1828.331536744552</v>
       </c>
       <c r="H4" t="n">
-        <v>13.68257971060883</v>
+        <v>4.79864651988131</v>
       </c>
       <c r="I4" t="n">
         <v>1828.331536744552</v>
       </c>
       <c r="J4" t="n">
-        <v>13.68257971060883</v>
+        <v>4.82641259339648</v>
       </c>
       <c r="K4" t="n">
         <v>1828.331536744552</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>11.6544026053454</v>
+        <v>4.757116543224582</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>1828.331536744552</v>
       </c>
       <c r="F5" t="n">
-        <v>11.54713229285424</v>
+        <v>4.834333849950005</v>
       </c>
       <c r="G5" t="n">
         <v>1828.331536744552</v>
       </c>
       <c r="H5" t="n">
-        <v>13.68257971060883</v>
+        <v>4.79864651988131</v>
       </c>
       <c r="I5" t="n">
         <v>1828.331536744552</v>
       </c>
       <c r="J5" t="n">
-        <v>13.68257971060883</v>
+        <v>4.82641259339648</v>
       </c>
       <c r="K5" t="n">
         <v>1828.331536744552</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>11.6544026053454</v>
+        <v>8.623852288577096</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>1828.331536744552</v>
       </c>
       <c r="F6" t="n">
-        <v>11.54713229285424</v>
+        <v>6.321195605097358</v>
       </c>
       <c r="G6" t="n">
         <v>1828.331536744552</v>
       </c>
       <c r="H6" t="n">
-        <v>13.68257971060883</v>
+        <v>7.940113720069661</v>
       </c>
       <c r="I6" t="n">
         <v>1828.331536744552</v>
       </c>
       <c r="J6" t="n">
-        <v>13.68257971060883</v>
+        <v>6.827163461620542</v>
       </c>
       <c r="K6" t="n">
         <v>1828.331536744552</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2.742497305116828</v>
+        <v>5.851439999999999</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001230743096470588</v>
+        <v>0.0008561691105882353</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001230743096470588</v>
+        <v>0.0008561691105882353</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001230743096470588</v>
+        <v>0.0008293801276281876</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001230743096470588</v>
+        <v>0.0008068633056562696</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.001016700818823532</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.00101670081882353</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.00101670081882353</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.001016700818823529</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.001016700818823531</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.001048427528408063</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.00101670081882353</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.001016700818823529</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.001016700818823532</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.001048427528408063</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.00101670081882353</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.001016700818823529</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.00101670081882353</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.001048427528408063</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.00101670081882353</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001284253665882353</v>
+        <v>0.00101670081882353</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.08977452573589814</v>
+        <v>0.05372036928873473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1063,19 +1063,19 @@
         <v>0.1910327328</v>
       </c>
       <c r="F17" t="n">
-        <v>0.08977452573589817</v>
+        <v>0.05372036928873473</v>
       </c>
       <c r="G17" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="H17" t="n">
-        <v>0.08977452573589877</v>
+        <v>0.04634185844491738</v>
       </c>
       <c r="I17" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08977452573589877</v>
+        <v>0.04503504675709507</v>
       </c>
       <c r="K17" t="n">
         <v>0.1910327328</v>
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.08977452573589814</v>
+        <v>0.05372036928873473</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,19 +1100,19 @@
         <v>0.1910327328</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08977452573589817</v>
+        <v>0.05372036928873473</v>
       </c>
       <c r="G18" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="H18" t="n">
-        <v>0.08977452573589877</v>
+        <v>0.04634185844491738</v>
       </c>
       <c r="I18" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="J18" t="n">
-        <v>0.08977452573589877</v>
+        <v>0.04503504675709507</v>
       </c>
       <c r="K18" t="n">
         <v>0.1910327328</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.08977452573589814</v>
+        <v>0.05372036928873473</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>0.1910327328</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08977452573589817</v>
+        <v>0.05372036928873473</v>
       </c>
       <c r="G19" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="H19" t="n">
-        <v>0.08977452573589877</v>
+        <v>0.04634185844491738</v>
       </c>
       <c r="I19" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="J19" t="n">
-        <v>0.08977452573589877</v>
+        <v>0.04503504675709507</v>
       </c>
       <c r="K19" t="n">
         <v>0.1910327328</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.085718616736699</v>
+        <v>0.0656680592739436</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>0.1910327328</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08571861673669902</v>
+        <v>0.06270670619805699</v>
       </c>
       <c r="G20" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="H20" t="n">
-        <v>0.085718616736699</v>
+        <v>0.02942738110039712</v>
       </c>
       <c r="I20" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="J20" t="n">
-        <v>0.085718616736699</v>
+        <v>0.02844924211755196</v>
       </c>
       <c r="K20" t="n">
         <v>0.1910327328</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.085718616736699</v>
+        <v>0.0656680592739436</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>0.1910327328</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08571861673669902</v>
+        <v>0.06270670619805699</v>
       </c>
       <c r="G21" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="H21" t="n">
-        <v>0.085718616736699</v>
+        <v>0.02942738110039712</v>
       </c>
       <c r="I21" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="J21" t="n">
-        <v>0.085718616736699</v>
+        <v>0.02844924211755196</v>
       </c>
       <c r="K21" t="n">
         <v>0.1910327328</v>
@@ -1419,7 +1419,7 @@
         <v>46023</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.039798486</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1433,19 +1433,19 @@
         <v>0.1910327328</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.039798486</v>
       </c>
       <c r="G27" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.04717699684381736</v>
       </c>
       <c r="I27" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.04848380853163967</v>
       </c>
       <c r="K27" t="n">
         <v>0.1910327328</v>
@@ -1456,7 +1456,7 @@
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.039798486</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1470,19 +1470,19 @@
         <v>0.1910327328</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.039798486</v>
       </c>
       <c r="G28" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.051169482</v>
       </c>
       <c r="I28" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.0510843854955819</v>
       </c>
       <c r="K28" t="n">
         <v>0.1910327328</v>
@@ -1493,7 +1493,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.04090045094791787</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1507,19 +1507,19 @@
         <v>0.1910327328</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.04114566716233972</v>
       </c>
       <c r="G29" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.05685497999999999</v>
       </c>
       <c r="I29" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.05676796607551848</v>
       </c>
       <c r="K29" t="n">
         <v>0.1910327328</v>
@@ -1530,7 +1530,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.02084837524559115</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,19 +1544,19 @@
         <v>0.1910327328</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.02380952380952381</v>
       </c>
       <c r="G30" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.05708905341913765</v>
       </c>
       <c r="I30" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.05806719240198278</v>
       </c>
       <c r="K30" t="n">
         <v>0.1910327328</v>
@@ -1567,7 +1567,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.02084837524559114</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,19 +1581,19 @@
         <v>0.1910327328</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.02380952380952381</v>
       </c>
       <c r="G31" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.05309656826295501</v>
       </c>
       <c r="I31" t="n">
         <v>0.1910327328</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.05546661543804057</v>
       </c>
       <c r="K31" t="n">
         <v>0.1910327328</v>
@@ -2142,13 +2142,13 @@
         <v>3.180153268219384</v>
       </c>
       <c r="H46" t="n">
-        <v>3.180153268219384</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>3.180153268219384</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>3.180153268219384</v>
       </c>
       <c r="K46" t="n">
         <v>3.180153268219384</v>
@@ -2381,7 +2381,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1585270019011556</v>
+        <v>0.1508859075205921</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2395,19 +2395,19 @@
         <v>0.5037968425936028</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1510353765649565</v>
+        <v>0.1493601596123783</v>
       </c>
       <c r="G53" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1484282284840849</v>
+        <v>0.1514569371141601</v>
       </c>
       <c r="I53" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="J53" t="n">
-        <v>0.158946148901166</v>
+        <v>0.1493029815743855</v>
       </c>
       <c r="K53" t="n">
         <v>0.5037968425936028</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.1585270019011556</v>
+        <v>0.1508859075205921</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>0.5037968425936028</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1510353765649565</v>
+        <v>0.1493601596123783</v>
       </c>
       <c r="G54" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1484282284840849</v>
+        <v>0.1514569371141601</v>
       </c>
       <c r="I54" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="J54" t="n">
-        <v>0.158946148901166</v>
+        <v>0.1493140856898931</v>
       </c>
       <c r="K54" t="n">
         <v>0.5037968425936028</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1585270019011556</v>
+        <v>0.1508859075205921</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>0.5037968425936028</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1510353765649565</v>
+        <v>0.1493601596123783</v>
       </c>
       <c r="G55" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1484282284840849</v>
+        <v>0.1514716328565549</v>
       </c>
       <c r="I55" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="J55" t="n">
-        <v>0.158946148901166</v>
+        <v>0.1493140856898931</v>
       </c>
       <c r="K55" t="n">
         <v>0.5037968425936028</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1730438000016513</v>
+        <v>0.1714018619127346</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>0.5037968425936028</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1580241723113533</v>
+        <v>0.158008478574145</v>
       </c>
       <c r="G56" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1516972644616576</v>
+        <v>0.167424902248231</v>
       </c>
       <c r="I56" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="J56" t="n">
-        <v>0.169356899079258</v>
+        <v>0.1609514363793784</v>
       </c>
       <c r="K56" t="n">
         <v>0.5037968425936028</v>
@@ -2751,7 +2751,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.06847592835406772</v>
+        <v>0.04671995893600184</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2765,19 +2765,19 @@
         <v>0.5037968425936028</v>
       </c>
       <c r="F63" t="n">
-        <v>0.07647038328006912</v>
+        <v>0.04805149385837602</v>
       </c>
       <c r="G63" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="H63" t="n">
-        <v>0.06906762159021615</v>
+        <v>0.04609676105574002</v>
       </c>
       <c r="I63" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="J63" t="n">
-        <v>0.05854970117313506</v>
+        <v>0.04784881034387109</v>
       </c>
       <c r="K63" t="n">
         <v>0.5037968425936028</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.06847592835406772</v>
+        <v>0.04671995893600184</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>0.5037968425936028</v>
       </c>
       <c r="F64" t="n">
-        <v>0.07647038328006912</v>
+        <v>0.04805149385837602</v>
       </c>
       <c r="G64" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="H64" t="n">
-        <v>0.06906762159021615</v>
+        <v>0.04609676105574002</v>
       </c>
       <c r="I64" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="J64" t="n">
-        <v>0.05854970117313506</v>
+        <v>0.04820557018335998</v>
       </c>
       <c r="K64" t="n">
         <v>0.5037968425936028</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.06847592835406772</v>
+        <v>0.04747092360244641</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>0.5037968425936028</v>
       </c>
       <c r="F65" t="n">
-        <v>0.07647038328006912</v>
+        <v>0.04842533450558018</v>
       </c>
       <c r="G65" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="H65" t="n">
-        <v>0.06906762159021616</v>
+        <v>0.04743137495312678</v>
       </c>
       <c r="I65" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="J65" t="n">
-        <v>0.05854970117313509</v>
+        <v>0.0495996879289451</v>
       </c>
       <c r="K65" t="n">
         <v>0.5037968425936028</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.07294921395208481</v>
+        <v>0.02873121589693458</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>0.5037968425936028</v>
       </c>
       <c r="F66" t="n">
-        <v>0.08847167123218512</v>
+        <v>0.05492891018587799</v>
       </c>
       <c r="G66" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="H66" t="n">
-        <v>0.08478866931115618</v>
+        <v>0.0401735429347906</v>
       </c>
       <c r="I66" t="n">
         <v>0.5037968425936028</v>
       </c>
       <c r="J66" t="n">
-        <v>0.06712903469355581</v>
+        <v>0.05346198194040819</v>
       </c>
       <c r="K66" t="n">
         <v>0.5037968425936028</v>
